--- a/automotive_forms/020_tire_replacement_requisition_form--automotive_forms.xlsx
+++ b/automotive_forms/020_tire_replacement_requisition_form--automotive_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -780,8 +780,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -809,12 +809,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'car'}</t>
+          <t>car</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Car'}</t>
+          <t>Car</t>
         </is>
       </c>
     </row>
@@ -826,12 +826,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'suv'}</t>
+          <t>suv</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'SUV'}</t>
+          <t>SUV</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'truck'}</t>
+          <t>truck</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Truck'}</t>
+          <t>Truck</t>
         </is>
       </c>
     </row>
@@ -860,12 +860,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_15}</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 15}</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -877,12 +877,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_16}</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 16}</t>
+          <t>16</t>
         </is>
       </c>
     </row>
@@ -894,12 +894,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_17}</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 17}</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_18}</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 18}</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -928,12 +928,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_19}</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 19}</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -945,12 +945,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_20}</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 20}</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -962,12 +962,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_7,_'label':_22}</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 7, 'label': 22}</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_8,_'label':_24}</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 8, 'label': 24}</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -996,12 +996,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_9,_'label':_26}</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 9, 'label': 26}</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -1013,12 +1013,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'new'}</t>
+          <t>new</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'New'}</t>
+          <t>New</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'used'}</t>
+          <t>used</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Used'}</t>
+          <t>Used</t>
         </is>
       </c>
     </row>
@@ -1047,12 +1047,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
